--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260910.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260910.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>9,800,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>15.59%</t>
+          <t>15.37%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>6.46%</t>
+          <t>6.68%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.09%</t>
+          <t>6.31%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.44%</t>
+          <t>5.51%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.31%</t>
+          <t>5.38%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.92%</t>
+          <t>5.02%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.06%</t>
+          <t>4.13%</t>
         </is>
       </c>
     </row>
@@ -770,95 +770,95 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.91%</t>
+          <t>3.96%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2,750,000</t>
+          <t>1,987,956</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>2.98%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2,307,000</t>
+          <t>2,750,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>2.95%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>1,987,956</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>2.93%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>2,307,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>2.90%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.58%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.31%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.11%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
@@ -968,117 +968,117 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>2,800,000</t>
+          <t>1,900,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.70%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>140,500</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.66%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>1,293,000</t>
+          <t>2,800,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>1,293,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>1,900,000</t>
+          <t>120,500</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1276,24 +1276,24 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>1,100,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,22 +1305,22 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,100,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
@@ -1437,44 +1437,44 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>1,500,000</t>
+          <t>386,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>386,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
@@ -1525,122 +1525,122 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>長興</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>1,500,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.07%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>長興</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1,500,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.06%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>350,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>350,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>6,895,086,642</t>
+          <t>7,010,382,185</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>3,152,903,551</t>
+          <t>2,579,837,073</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>4,074,325,080</t>
+          <t>3,474,325,080</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
